--- a/data/trans_dic/IP31C_R_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31C_R_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>2,43; 12,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,62</t>
+          <t>3,01; 19,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,73</t>
+          <t>3,34; 11,92</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 8,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,58; 6,1</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,94; 31,27</t>
+          <t>7,0; 21,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 20,65</t>
+          <t>14,5; 33,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 22,67</t>
+          <t>11,7; 24,71</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5,06; 19,64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2,93; 16,29</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,2</t>
+          <t>2,67; 10,05</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 12,89</t>
+          <t>8,34; 19,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 17,49</t>
+          <t>6,17; 15,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,9; 13,61</t>
+          <t>8,16; 15,13</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,07; 22,36</t>
+          <t>15,56; 28,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,79; 26,42</t>
+          <t>11,08; 22,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,46; 22,71</t>
+          <t>15,18; 23,6</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,56; 9,38</t>
+          <t>8,8; 13,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,84</t>
+          <t>7,49; 11,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,89; 9,62</t>
+          <t>8,71; 11,83</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>13721</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7007</t>
+          <t>2780; 13794</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>949; 9594</t>
+          <t>2992; 19039</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2235; 11894</t>
+          <t>7141; 25501</t>
         </is>
       </c>
     </row>
@@ -1234,17 +1234,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>2840</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5268</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2650</t>
+          <t>0; 4571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3432</t>
+          <t>646; 6791</t>
         </is>
       </c>
     </row>
@@ -1307,17 +1307,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>25183</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9635; 21617</t>
+          <t>4888; 15104</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4046; 15560</t>
+          <t>10149; 23303</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15729; 32764</t>
+          <t>16358; 34542</t>
         </is>
       </c>
     </row>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>3356</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>4195</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2002; 7774</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1191; 6632</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1179; 6892</t>
+          <t>2001; 7529</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>635</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>635</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3442</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4268</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3026</t>
+          <t>0; 3060</t>
         </is>
       </c>
     </row>
@@ -1526,17 +1526,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>18190</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27836</t>
+          <t>30166</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5691; 15857</t>
+          <t>11646; 26894</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11520; 26978</t>
+          <t>7477; 19014</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19119; 37740</t>
+          <t>21296; 39484</t>
         </is>
       </c>
     </row>
@@ -1599,17 +1599,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>20470</t>
+          <t>33627</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>56104</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14148; 28572</t>
+          <t>24369; 44392</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>22713; 40582</t>
+          <t>15194; 31346</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40690; 63891</t>
+          <t>44584; 69321</t>
         </is>
       </c>
     </row>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>132844</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>36228; 61083</t>
+          <t>60289; 90234</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>52179; 80544</t>
+          <t>46171; 73643</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96021; 134031</t>
+          <t>113299; 153988</t>
         </is>
       </c>
     </row>
